--- a/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_rule_text.xlsx
+++ b/engine_package/Res/MuDataEditor/天使之战_v1.0.0.0/Out/cfg_rule_text.xlsx
@@ -9,6 +9,7 @@
   <sheets>
     <sheet name="cfg_fruit" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="128">
   <si>
     <t>ID</t>
   </si>
@@ -75,6 +76,102 @@
     <t>location</t>
   </si>
   <si>
+    <t>红名系统</t>
+  </si>
+  <si>
+    <t>1、玩家击杀&lt;color=#2EED36&gt;其他非红名玩家&lt;/color&gt;时会增加pk值，当PK获得累计到一定量时，玩家就会变为&lt;color=#ED2E2E&gt;红名状态&lt;/color&gt;\n2、红名状态惩罚：限制使用&lt;color=#ED2E2E&gt;传送功能&lt;/color&gt;、限制使用&lt;color=#ED2E2E&gt;商店购买&lt;/color&gt;补给、pk值较高时无法&lt;color=#ED2E2E&gt;对玩家造成伤害&lt;/color&gt;\n3、恶人状态清洗，PK值会随&lt;color=#2EED36&gt;时间流逝而减少&lt;/color&gt;，玩家也可通过&lt;color=#ED2E2E&gt;击杀怪物&lt;/color&gt;、&lt;color=#ED2E2E&gt;使用道具&lt;/color&gt;等方式清除自身拥有的PK值\n4、防卫状态，在被其他玩家攻击时存在&lt;color=#ED2E2E&gt;防卫反击时间&lt;/color&gt;，若在防卫反击时间内将攻击方击杀则被攻击方不会增加PK值</t>
+  </si>
+  <si>
+    <t>组队</t>
+  </si>
+  <si>
+    <t>说 明</t>
+  </si>
+  <si>
+    <t>1、队伍最大人数为5人。同职业最多限制2个\n2、组队打怪时，获得怪物的经验会&lt;color=#00FF00&gt;平分&lt;/color&gt;给&lt;color=#00FF00&gt;附近战斗&lt;/color&gt;的每位队员\n3、队伍人数越多获得的经验加成比例越高，每增加一位成员增加&lt;color=#00FF00&gt;30%&lt;/color&gt;经验加成\n4、申请队伍后需队长同意才能入队。</t>
+  </si>
+  <si>
+    <t>果实系统</t>
+  </si>
+  <si>
+    <t>果实</t>
+  </si>
+  <si>
+    <t>1、果实可为玩家增加基础属性\n2、使用果实后增加的数值为1-3随机值\n3、</t>
+  </si>
+  <si>
+    <t>邮件</t>
+  </si>
+  <si>
+    <t>1、邮件最多保存15天，请及时处理。\n2、当背包不足时，无法领取邮件。</t>
+  </si>
+  <si>
+    <t>狼人要塞</t>
+  </si>
+  <si>
+    <t>狼魂要塞</t>
+  </si>
+  <si>
+    <t>1、活动前5分钟为准备阶段，盟主和副盟主可以消耗战盟资金召唤弓箭手，最多召唤5个。\n2、活动总计10波怪物，击杀完所有怪物或者活动时间结束则守卫成功，狼魂雕像被摧毁则守卫失败。\n3、击杀完一波怪物可以获得战盟经验奖励。\n4、每波怪物有几率生成精英怪物，击杀精英怪物可以获得一次学习天赋的机会。\n5、每个方阵的怪物有概率拥有特殊词缀，词缀会提升怪物的能力。</t>
+  </si>
+  <si>
+    <t>攻城战</t>
+  </si>
+  <si>
+    <t>参与方式</t>
+  </si>
+  <si>
+    <t>活动期间进入罗兰峡谷即可参与\n盟主需要先进入罗兰攻城战内</t>
+  </si>
+  <si>
+    <t>开启时间</t>
+  </si>
+  <si>
+    <t>每周六的20：00~20：30</t>
+  </si>
+  <si>
+    <t>胜利条件</t>
+  </si>
+  <si>
+    <t>1.摧毁所有城门、守护石像后，占领罗伦之冠，占领区仅剩1个战盟时，可进行占领\n2.当无任何战盟有占领权时，战盟积分排名第1直接获胜，但是无法成为下次攻城战的守方，盟主也不会出现在名人堂。\n攻城方可获得积分:摧毁建筑、击杀敌人、对敌入造成伤害或治疗队友\n守城方可获得积分:持续守护罗伦之冠、击杀敌人、对敌人造成伤害或治疗队友</t>
+  </si>
+  <si>
+    <t>注意事项</t>
+  </si>
+  <si>
+    <t>1.占领龙之塔内的罗伦之冠后，攻城战也不会因此而结束，攻城时间结束时，最后占领罗伦之冠的战盟才算最后胜利的战盟\n2.每层守护石像被攻破后，攻城方的出生点会变化，建议防守方提早进入城池\n3.攻城战期间，无法进行战盟职位变更，无法加入或退出战盟\n4.每次攻城战开启时，系统自动收回上次发放的称号\n5.攻城战结束后将通过邮件发放称号奖励、积分奖励，</t>
+  </si>
+  <si>
+    <t>攻城战说明</t>
+  </si>
+  <si>
+    <t>1、攻城战共分为&lt;color=#00FF00&gt;4个阶段&lt;/color&gt;。\n2、1~3阶段，玩家分为&lt;color=#00FF00&gt;攻方和守方&lt;/color&gt;两个阵营；攻方针对城门进行进攻方案，攻破外城门、中城门、内城门后，即可进行下一阶段的任务；守方则在对应的阶段，守住城门，抵抗攻方。\n3、4阶段时，玩家不在按照攻守方进行阵营划分，而是&lt;color=#00FF00&gt;每个战盟为一个独立的阵营&lt;/color&gt;；玩家需要前往&lt;color=#00FF00&gt;龙之塔&lt;/color&gt;，占领&lt;color=#00FF00&gt;罗兰之冠&lt;/color&gt;，为自己的战盟夺得胜利！</t>
+  </si>
+  <si>
+    <t>面对面交易</t>
+  </si>
+  <si>
+    <t>1、面对面交易货币税率为9%\n2、面对面交易双方需要在一定距离内进行\n3、面对面交易存在限制，需要开通畅玩卡\n4、货币必须为支持面对面交易的道具且为非绑物品\n5、交易存在交易时间，超过时间交易超时将关闭界面\n6、交易确认环节后任意一方解锁交易栏，双方均会解锁</t>
+  </si>
+  <si>
+    <t>卡利玛神庙</t>
+  </si>
+  <si>
+    <t>1、副本地图，每日可进入5次，副本限时60分钟。\n2、每次进入卡利玛神庙需要消耗对应积分。\n3、击杀boss昆顿后，人物将在30s后自动离开副本\n4、卡利玛神庙内怪物较少、击杀后不会重生，但是爆率极高，最低掉落卓越品质装备，套装，卓越套装唯一产出。</t>
+  </si>
+  <si>
+    <t>&lt;color=#1ADD1F&gt;</t>
+  </si>
+  <si>
+    <t>&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>1、积分奖励\n积分奖励勋章为&lt;color=#1ADD1F&gt;动态显示&lt;/color&gt;，显示勋章数量为实际可获得的数量\n有该档位排名后，才会显示该排名段的奖励预览\n2、杀怪积分转化详情\n&lt;color=#1ADD1F&gt;0分&lt;/color&gt;到&lt;color=#1ADD1F&gt;350000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;60%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;350000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;690000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;100%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;690000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;1380000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;130%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;1380000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;2070000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;160%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;2070000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;3110000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;180%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;3110000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;4150000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;200%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;4150000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;5530000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;220%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;5530000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;6910000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;240%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;6910000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;8640000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;260%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;8640000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;10370000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;280%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;10370000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;12440000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;300%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;12440000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;15210000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;310%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;15210000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;17980000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;320%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;17980000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;21430000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;330%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;21430000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;25580000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;340%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;25580000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;31800000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;350%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;31800000分&lt;/color&gt;以上，转化比率为：&lt;color=#1ADD1F&gt;360%&lt;/color&gt;</t>
+  </si>
+  <si>
+    <t>&lt;color=#1ADD1F&gt;0分&lt;/color&gt;到&lt;color=#1ADD1F&gt;350000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;60%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;350000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;690000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;100%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;690000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;1380000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;130%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;1380000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;2070000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;160%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;2070000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;3110000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;180%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;3110000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;4150000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;200%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;4150000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;5530000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;220%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;5530000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;6910000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;240%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;6910000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;8640000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;260%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;8640000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;10370000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;280%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;10370000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;12440000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;300%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;12440000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;15210000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;310%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;15210000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;17980000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;320%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;17980000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;21430000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;330%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;21430000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;25580000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;340%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;25580000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;31800000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;350%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;31800000分&lt;/color&gt;以上，转化比率为：&lt;color=#1ADD1F&gt;360%&lt;/color&gt;</t>
+  </si>
+  <si>
     <t>萤石</t>
   </si>
   <si>
@@ -96,9 +193,6 @@
     <t>1、所有套装都可以被分解，分解后装备消失\n2、套装分解后会获得粉尘，粉尘可合成镶嵌宝石\n3、有强化、追加等级的装备分解后不会返还强化材料，请谨慎</t>
   </si>
   <si>
-    <t>红名系统</t>
-  </si>
-  <si>
     <t>1、玩家击杀&lt;color=#2EED36&gt;其他非红名玩家&lt;/color&gt;时会增加pk值，当PK获得累计到一定量时，玩家就会变为&lt;color=#ED2E2E&gt;恶人状态&lt;/color&gt;\n2、恶人状态惩罚：限制使用&lt;color=#ED2E2E&gt;传送功能&lt;/color&gt;、限制使用&lt;color=#ED2E2E&gt;商店购买&lt;/color&gt;补给、pk值较高时无法&lt;color=#ED2E2E&gt;对玩家造成伤害&lt;/color&gt;\n3、恶人状态清洗，PK值会随&lt;color=#2EED36&gt;时间流逝而减少&lt;/color&gt;，玩家也可通过&lt;color=#ED2E2E&gt;击杀怪物&lt;/color&gt;、&lt;color=#ED2E2E&gt;使用道具&lt;/color&gt;等方式清除自身拥有的PK值\n4、防卫状态，在被其他玩家攻击时存在&lt;color=#ED2E2E&gt;防卫反击时间&lt;/color&gt;，若在防卫反击时间内将攻击方击杀则被攻击方不会增加PK值</t>
   </si>
   <si>
@@ -120,12 +214,6 @@
     <t>1、可以消耗月卡时间兑换&lt;color=#00FF00&gt;黄金特权&lt;/color&gt;或&lt;color=#00FF00&gt;钻石特权&lt;/color&gt;获取超额收益。，\n2、使用&lt;color=#00FF00&gt;黄金特权卡&lt;/color&gt;后激活30天&lt;color=#E6E600&gt;黄金特权&lt;/color&gt;，\n激活后可获得以下特权，\n&lt;color=#00FF00&gt;·开启黄金线&lt;/color&gt;，\n&lt;color=#00FF00&gt;·黄金线中额外享受50%的经验、掉落加成&lt;/color&gt;，\n&lt;color=#00FF00&gt;·开启小怪挂机保护功能&lt;/color&gt;，\n&lt;color=#00FF00&gt;·背包空间增加160格&lt;/color&gt;，\n&lt;color=#00FF00&gt;·开启自动买药&lt;/color&gt;，\n&lt;color=#00FF00&gt;·开启随身商店功能&lt;/color&gt;，\n&lt;color=#00FF00&gt;·开启加点方案切换&lt;/color&gt;，\n3、使用&lt;color=#00FF00&gt;钻石特权卡&lt;/color&gt;后激活30天&lt;color=#E6E600&gt;钻石特权&lt;/color&gt;，\n激活后可获得以下特权，\n&lt;color=#00FF00&gt;·装备掉率增加100%&lt;/color&gt;，\n&lt;color=#00FF00&gt;·怪物经验增加100%&lt;/color&gt;，\n&lt;color=#00FF00&gt;·奇迹而回收价增加30%&lt;/color&gt;，\n&lt;color=#00FF00&gt;·开启黄金怪挂机功能&lt;/color&gt;，\n&lt;color=#00FF00&gt;·背包空间增加320格&lt;/color&gt;，\n&lt;color=#00FF00&gt;·开启远程仓库&lt;/color&gt;，\n&lt;color=#00FF00&gt;·增加交易行寄售格子5格&lt;/color&gt;，</t>
   </si>
   <si>
-    <t>组队</t>
-  </si>
-  <si>
-    <t>说 明</t>
-  </si>
-  <si>
     <t>1、队伍最大人数为5人。\n2、组队打怪时，获得怪物的经验会&lt;color=#00FF00&gt;平分&lt;/color&gt;给&lt;color=#00FF00&gt;附近战斗&lt;/color&gt;的每位队员\n3、队伍人数越多获得的经验加成比例越高，每增加一位成员增加&lt;color=#00FF00&gt;30%&lt;/color&gt;经验加成\n4、申请队伍后需队长同意才能入队。</t>
   </si>
   <si>
@@ -144,12 +232,6 @@
     <t>1、只有卓越套装可以使用套装叠加功能。\n2、可以将副装备上拥有但主装备上没有的卓越属性附加在主装备上。\n3、每次叠加只可以把&lt;color=#00FF00&gt;副装备中的一条卓越属性附加到主装备上&lt;/color&gt;。\n4、一般装备最多可以叠加获得最多&lt;color=#00FF00&gt;4条卓越词条&lt;/color&gt;。\n5、当装备词条达到最大数量后，继续叠加可以&lt;color=#00FF00&gt;随机替换&lt;/color&gt;一个&lt;color=#00FF00&gt;卓越词条&lt;/color&gt;，被锁定的词条无法被替换。\n6、可消耗幸运宝石&lt;color=#00FF00&gt;提升叠加成功率&lt;/color&gt;。\n7、装备叠加后获得的装备将保留两件装备中等级最高的强化和追加值。</t>
   </si>
   <si>
-    <t>果实系统</t>
-  </si>
-  <si>
-    <t>果实</t>
-  </si>
-  <si>
     <t>1、果实可为玩家增加基础属性\n2、使用果实后增加的数值为随机值\n3、玩家可消耗奇迹币进行点数重置，重置后的点数可自由增加。</t>
   </si>
   <si>
@@ -180,9 +262,6 @@
     <t>·激活后，可获得&lt;color=#00FF00&gt;连击技能&lt;/color&gt;，使用技能时，可获得连击值，连击值满时，&lt;color=#00FF00&gt;自动&lt;/color&gt;释放连击技能。</t>
   </si>
   <si>
-    <t>邮件</t>
-  </si>
-  <si>
     <t>1、邮件最多保存15天，请及时处理邮件，谨防丢失。\n2、全部领取：一次性领取所有邮件中的附件。\n3、全部删除：一次性删除所有邮件。\n4、当背包不足时，无法领取邮件。</t>
   </si>
   <si>
@@ -261,48 +340,9 @@
     <t>1、抽奖是消耗钻石随机获取奖池奖励的玩法，每次抽取必定会获得奖池内任意一份奖励\n2、奖池内的高品质奖励有可抽到次数限制，抽完后将从奖池内消失\n3、抽奖有免费次数，使用后自动进入倒计时，倒计时结束后免费次数刷新\n4、抽奖有额外奖励，根据在当前奖池的总抽数解锁领取\n5、当期奖池活动结束后，抽奖计数等都将清空，不会累计到下次抽奖活动中，请及时累计次数，获取超值大奖！</t>
   </si>
   <si>
-    <t>狼人要塞</t>
-  </si>
-  <si>
-    <t>狼魂要塞</t>
-  </si>
-  <si>
-    <t>1、活动前5分钟为准备阶段，盟主和副盟主可以消耗战盟资金召唤弓箭手，最多召唤5个。\n2、活动总计10波怪物，击杀完所有怪物或者活动时间结束则守卫成功，狼魂雕像被摧毁则守卫失败。\n3、击杀完一波怪物可以获得战盟经验奖励。\n4、每波怪物有几率生成精英怪物，击杀精英怪物可以获得一次学习天赋的机会。\n5、每个方阵的怪物有概率拥有特殊词缀，词缀会提升怪物的能力。</t>
-  </si>
-  <si>
-    <t>攻城战</t>
-  </si>
-  <si>
-    <t>参与方式</t>
-  </si>
-  <si>
-    <t>活动期间进入罗兰峡谷即可参与\n盟主需要先进入罗兰攻城战内</t>
-  </si>
-  <si>
-    <t>开启时间</t>
-  </si>
-  <si>
-    <t>每周三和周六的20：00~20：30</t>
-  </si>
-  <si>
-    <t>胜利条件</t>
-  </si>
-  <si>
     <t>1.摧毁所有城门、守护石像后，进入龙之塔占领罗伦之冠，占领区仅剩1个战盟时，可进行占领\n2.当无任何战盟有占领权时，战盟积分排名第1直接获胜，但是无法成为下次攻城战的守方，盟主也不会出现在名人堂。\n攻城方可获得积分:摧毁建筑、击杀敌人、对敌入造成伤害或治疗队友\n守城方可获得积分:持续守护罗伦之冠、击杀敌人、对敌人造成伤害或治疗队友</t>
   </si>
   <si>
-    <t>注意事项</t>
-  </si>
-  <si>
-    <t>1.占领龙之塔内的罗伦之冠后，攻城战也不会因此而结束，攻城时间结束时，最后占领罗伦之冠的战盟才算最后胜利的战盟\n2.每层守护石像被攻破后，攻城方的出生点会变化，建议防守方提早进入城池\n3.攻城战期间，无法进行战盟职位变更，无法加入或退出战盟\n4.每次攻城战开启时，系统自动收回上次发放的称号\n5.攻城战结束后将通过邮件发放称号奖励、积分奖励，</t>
-  </si>
-  <si>
-    <t>攻城战说明</t>
-  </si>
-  <si>
-    <t>1、攻城战共分为&lt;color=#00FF00&gt;4个阶段&lt;/color&gt;。\n2、1~3阶段，玩家分为&lt;color=#00FF00&gt;攻方和守方&lt;/color&gt;两个阵营；攻方针对城门进行进攻方案，攻破外城门、中城门、内城门后，即可进行下一阶段的任务；守方则在对应的阶段，守住城门，抵抗攻方。\n3、4阶段时，玩家不在按照攻守方进行阵营划分，而是&lt;color=#00FF00&gt;每个战盟为一个独立的阵营&lt;/color&gt;；玩家需要前往&lt;color=#00FF00&gt;龙之塔&lt;/color&gt;，占领&lt;color=#00FF00&gt;罗兰之冠&lt;/color&gt;，为自己的战盟夺得胜利！</t>
-  </si>
-  <si>
     <t>大秘境</t>
   </si>
   <si>
@@ -363,9 +403,6 @@
     <t>1、开启时间:从14:00开始，每2小时开启一场一天总开启6场。\n2、不同等级可进入不同层恶魔广场，每次进入恶魔广场需消耗对应数量的恶魔通行证。\n3、恶魔广场内怪物密集、刷新频率高、击杀怪物经验多，此副本内挂机打怪可获得大量经验。\n4.恶魔广场可组队进入，击杀怪物均分经验。\n5.组队进入恶魔广场后，击杀怪物可获得积分，结算时根据积分可获得额外奖励。\n6.根据积分数量对组队成员进行排名，恶魔广场结算时根据排名前三名可获得额外奖励。</t>
   </si>
   <si>
-    <t>面对面交易</t>
-  </si>
-  <si>
     <t>1、面对面交易货币税率为10%\n2、面对面交易双方需要在一定距离内进行\n3、面对面交易存在特权限制，需要开通特权\n4、进行交易的道具与货币必须为支持面对面交易的道具且为非绑状态\n5、交易存在最大交易时间，超过这个时间交易超时将关闭界面\n6、进入交易确认环节后任意一方解锁交易栏，双方均会解锁</t>
   </si>
   <si>
@@ -375,22 +412,7 @@
     <t>1.使用：&lt;color=#1add1f&gt;更高级的药水&lt;/color&gt;\n\n2.提升：&lt;color=#1add1f&gt;防御值&lt;/color&gt;\n\n3.提升：&lt;color=#1add1f&gt;生命恢复速度&lt;/color&gt;\n\n4.提升：&lt;color=#1add1f&gt;最大生命值&lt;/color&gt;\n\n5.提升：&lt;color=#1add1f&gt;伤害减少&lt;/color&gt;，&lt;color=#1add1f&gt;伤害吸收&lt;/color&gt;</t>
   </si>
   <si>
-    <t>卡利玛神庙</t>
-  </si>
-  <si>
-    <t>1、&lt;color=#1add1f&gt;单人副本&lt;/color&gt;，每日可进入5次，&lt;color=#1add1f&gt;会员玩家可获得额外进入次数&lt;/color&gt;，副本限时60分钟。\n2、每次进入卡利玛神庙需要消耗对应积分&lt;/color&gt;。\n3、击杀boss昆顿后，人物将在&lt;color=#1add1f&gt;30s&lt;/color&gt;后自动离开副本\n4、卡利玛神庙内怪物较少、击杀后不会重生，但是爆率极高，最低掉落卓越品质装备，在卡利玛神庙有更高几率获得优质装备。\n5、击杀困顿获得Boss昆顿的掉落奖励。</t>
-  </si>
-  <si>
-    <t>&lt;color=#1ADD1F&gt;</t>
-  </si>
-  <si>
-    <t>&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>1、积分奖励\n积分奖励勋章为&lt;color=#1ADD1F&gt;动态显示&lt;/color&gt;，显示勋章数量为实际可获得的数量\n有该档位排名后，才会显示该排名段的奖励预览\n2、杀怪积分转化详情\n&lt;color=#1ADD1F&gt;0分&lt;/color&gt;到&lt;color=#1ADD1F&gt;350000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;60%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;350000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;690000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;100%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;690000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;1380000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;130%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;1380000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;2070000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;160%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;2070000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;3110000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;180%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;3110000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;4150000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;200%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;4150000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;5530000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;220%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;5530000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;6910000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;240%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;6910000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;8640000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;260%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;8640000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;10370000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;280%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;10370000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;12440000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;300%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;12440000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;15210000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;310%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;15210000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;17980000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;320%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;17980000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;21430000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;330%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;21430000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;25580000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;340%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;25580000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;31800000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;350%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;31800000分&lt;/color&gt;以上，转化比率为：&lt;color=#1ADD1F&gt;360%&lt;/color&gt;</t>
-  </si>
-  <si>
-    <t>&lt;color=#1ADD1F&gt;0分&lt;/color&gt;到&lt;color=#1ADD1F&gt;350000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;60%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;350000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;690000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;100%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;690000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;1380000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;130%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;1380000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;2070000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;160%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;2070000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;3110000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;180%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;3110000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;4150000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;200%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;4150000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;5530000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;220%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;5530000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;6910000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;240%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;6910000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;8640000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;260%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;8640000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;10370000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;280%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;10370000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;12440000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;300%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;12440000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;15210000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;310%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;15210000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;17980000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;320%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;17980000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;21430000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;330%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;21430000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;25580000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;340%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;25580000分&lt;/color&gt;到&lt;color=#1ADD1F&gt;31800000分&lt;/color&gt;段，转化比率为：&lt;color=#1ADD1F&gt;350%&lt;/color&gt;\n&lt;color=#1ADD1F&gt;31800000分&lt;/color&gt;以上，转化比率为：&lt;color=#1ADD1F&gt;360%&lt;/color&gt;</t>
+    <t>1、单人副本，每日可进入5次，副本限时60分钟。\n2、每次进入卡利玛神庙需要消耗对应积分。\n3、击杀boss昆顿后，人物将在30s后自动离开副本\n4、卡利玛神庙内怪物较少、击杀后不会重生，但是爆率极高，最低掉落卓越品质装备，在卡利玛神庙有更高几率获得优质装备。\n5、击杀困顿获得Boss昆顿的掉落奖励。</t>
   </si>
 </sst>
 </file>
@@ -1027,10 +1049,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
     <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -1577,673 +1599,247 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
   <cols>
-    <col min="1" max="1" width="19.875" style="2" customWidth="1"/>
-    <col min="2" max="2" width="15.375" style="2" customWidth="1"/>
-    <col min="3" max="3" width="34.5" style="2" customWidth="1"/>
-    <col min="4" max="4" width="86.75" style="1" customWidth="1"/>
-    <col min="5" max="6" width="19.25" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="1" max="1" width="19.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="86.75" style="2" customWidth="1"/>
+    <col min="5" max="6" width="19.25" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="2" customFormat="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="1" customFormat="1" spans="1:6">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="2" s="2" customFormat="1" spans="1:4">
-      <c r="A2" s="2" t="s">
+    <row r="2" s="1" customFormat="1" spans="1:6">
+      <c r="A2" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="3" s="2" customFormat="1" spans="1:4">
-      <c r="A3" s="2" t="s">
+    <row r="3" s="1" customFormat="1" spans="1:6">
+      <c r="A3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="2" t="s">
+      <c r="C3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" s="2" customFormat="1" spans="1:4">
-      <c r="A4" s="2" t="s">
+    <row r="4" s="1" customFormat="1" spans="1:6">
+      <c r="A4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="2" t="s">
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="5" s="2" customFormat="1" spans="1:4">
+    <row r="5" s="1" customFormat="1" spans="1:6">
       <c r="A5" s="3">
-        <v>1</v>
-      </c>
-      <c r="B5" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D5" s="4" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="6" s="2" customFormat="1" spans="1:4">
-      <c r="A6" s="3">
-        <v>2</v>
-      </c>
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="1:6">
+      <c r="A6" s="1">
+        <v>8</v>
+      </c>
+      <c r="B6" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="C6" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D6" s="4" t="s">
+      <c r="C6" s="1" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="7" s="2" customFormat="1" spans="1:4">
-      <c r="A7" s="3">
-        <v>3</v>
-      </c>
-      <c r="B7" s="2" t="s">
+      <c r="D6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C7" s="2" t="s">
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="1">
+        <v>11</v>
+      </c>
+      <c r="B7" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="C7" s="1" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="8" s="2" customFormat="1" spans="1:4">
-      <c r="A8" s="3">
-        <v>4</v>
-      </c>
-      <c r="B8" s="2" t="s">
+      <c r="D7" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="D8" s="4" t="s">
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="1">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="9" s="2" customFormat="1" spans="1:4">
-      <c r="A9" s="3">
-        <v>5</v>
-      </c>
-      <c r="B9" s="2" t="s">
+      <c r="C8" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D8" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D9" s="4" t="s">
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="1">
+        <v>15001</v>
+      </c>
+      <c r="B9" s="1" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="A10" s="2">
-        <v>6</v>
-      </c>
-      <c r="B10" s="2" t="s">
+      <c r="C9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="C10" s="2" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="2">
-        <v>7</v>
-      </c>
-      <c r="B11" s="2" t="s">
+    <row r="10" customFormat="1" spans="1:6">
+      <c r="A10" s="1">
+        <v>16001</v>
+      </c>
+      <c r="B10" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="1">
+        <v>16002</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D11" s="1" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="2">
-        <v>8</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>30</v>
-      </c>
-      <c r="C12" s="2" t="s">
+      <c r="C11" s="1" t="s">
         <v>31</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D11" s="2" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2">
-        <v>9</v>
-      </c>
-      <c r="B13" s="2" t="s">
+    <row r="12" spans="1:6">
+      <c r="A12" s="1">
+        <v>16003</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="D12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D13" s="1" t="s">
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="1">
+        <v>16004</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="A14" s="2">
-        <v>10</v>
-      </c>
-      <c r="B14" s="2" t="s">
+      <c r="D13" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="D14" s="1" t="s">
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:6">
+      <c r="A14" s="1">
+        <v>16005</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C14" s="1" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="2">
-        <v>11</v>
-      </c>
-      <c r="B15" s="2" t="s">
+      <c r="D14" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="C15" s="2" t="s">
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="1">
+        <v>33001</v>
+      </c>
+      <c r="B15" s="1" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="C15" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D15" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="2">
-        <v>12</v>
-      </c>
-      <c r="B16" s="2" t="s">
+    <row r="16" customFormat="1" spans="1:6">
+      <c r="A16" s="1">
+        <v>401</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>41</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="4" t="s">
-        <v>43</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17" s="2">
-        <v>13</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="D17" s="1" t="s">
-        <v>46</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18" s="2">
-        <v>14</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19" s="2">
-        <v>15</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D19" s="1" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20" s="2">
-        <v>101</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>52</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="D20" s="1" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21" s="2">
-        <v>102</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22" s="2">
-        <v>103</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D22" s="1" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6">
-      <c r="A23" s="2">
-        <v>104</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="D23" s="1" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6">
-      <c r="A24" s="2">
-        <v>105</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="D24" s="1" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6">
-      <c r="A25" s="2">
-        <v>201</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="D25" s="1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6">
-      <c r="A26" s="2">
-        <v>202</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>69</v>
-      </c>
-      <c r="D26" s="1" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6">
-      <c r="A27" s="2">
-        <v>203</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>71</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>72</v>
-      </c>
-      <c r="D27" s="1" t="s">
-        <v>73</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6">
-      <c r="A28" s="2">
-        <v>301</v>
-      </c>
-      <c r="B28" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>75</v>
-      </c>
-      <c r="D28" s="1" t="s">
-        <v>76</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6">
-      <c r="A29" s="2">
-        <v>15001</v>
-      </c>
-      <c r="B29" s="2" t="s">
-        <v>77</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>79</v>
-      </c>
-    </row>
-    <row r="30" customFormat="1" spans="1:6">
-      <c r="A30" s="2">
-        <v>16001</v>
-      </c>
-      <c r="B30" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>81</v>
-      </c>
-      <c r="D30" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="E30" s="2"/>
-      <c r="F30" s="2"/>
-    </row>
-    <row r="31" spans="1:6">
-      <c r="A31" s="2">
-        <v>16002</v>
-      </c>
-      <c r="B31" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>83</v>
-      </c>
-      <c r="D31" s="1" t="s">
-        <v>84</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6">
-      <c r="A32" s="2">
-        <v>16003</v>
-      </c>
-      <c r="B32" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6">
-      <c r="A33" s="2">
-        <v>16004</v>
-      </c>
-      <c r="B33" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>87</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="34" s="2" customFormat="1" spans="1:6">
-      <c r="A34" s="2">
-        <v>16005</v>
-      </c>
-      <c r="B34" s="2" t="s">
-        <v>80</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="35" spans="1:6">
-      <c r="A35" s="2">
-        <v>19001</v>
-      </c>
-      <c r="B35" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D35" s="1" t="s">
-        <v>92</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6">
-      <c r="A36" s="2">
-        <v>19002</v>
-      </c>
-      <c r="B36" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>93</v>
-      </c>
-      <c r="D36" s="1" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="37" s="2" customFormat="1" spans="1:6">
-      <c r="A37" s="2">
-        <v>27001</v>
-      </c>
-      <c r="B37" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="D37" s="1" t="s">
-        <v>96</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6">
-      <c r="A38" s="2">
-        <v>27002</v>
-      </c>
-      <c r="B38" s="2" t="s">
-        <v>95</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>97</v>
-      </c>
-      <c r="D38" s="1" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6">
-      <c r="A39" s="2">
-        <v>28001</v>
-      </c>
-      <c r="B39" s="2" t="s">
-        <v>99</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>100</v>
-      </c>
-      <c r="D39" s="1" t="s">
-        <v>101</v>
-      </c>
-    </row>
-    <row r="40" spans="1:6">
-      <c r="A40" s="2">
-        <v>29001</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>102</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D40" s="1" t="s">
-        <v>104</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6">
-      <c r="A41" s="2">
-        <v>30001</v>
-      </c>
-      <c r="B41" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="C41" s="2" t="s">
-        <v>105</v>
-      </c>
-      <c r="D41" s="1" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6">
-      <c r="A42" s="2">
-        <v>31001</v>
-      </c>
-      <c r="B42" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="C42" s="2" t="s">
-        <v>107</v>
-      </c>
-      <c r="D42" s="1" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6">
-      <c r="A43" s="2">
-        <v>32001</v>
-      </c>
-      <c r="B43" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="C43" s="2" t="s">
-        <v>109</v>
-      </c>
-      <c r="D43" s="1" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="44" spans="1:6">
-      <c r="A44" s="2">
-        <v>33001</v>
-      </c>
-      <c r="B44" s="2" t="s">
-        <v>111</v>
-      </c>
-      <c r="C44" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="D44" s="1" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6">
-      <c r="A45" s="2">
-        <v>34001</v>
-      </c>
-      <c r="B45" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="C45" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="D45" s="1" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="46" customFormat="1" spans="1:6">
-      <c r="A46" s="2">
-        <v>401</v>
-      </c>
-      <c r="B46" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="D46" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" s="2"/>
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E5:F5">
-    <cfRule type="duplicateValues" dxfId="0" priority="7"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E6:F6">
-    <cfRule type="duplicateValues" dxfId="0" priority="6"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E9:F9">
-    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E7:F8">
     <cfRule type="duplicateValues" dxfId="0" priority="5"/>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2259,26 +1855,703 @@
   <sheetData>
     <row r="1" spans="7:7">
       <c r="G1" t="s">
-        <v>117</v>
+        <v>43</v>
       </c>
     </row>
     <row r="2" spans="7:7">
       <c r="G2" t="s">
-        <v>118</v>
+        <v>44</v>
       </c>
     </row>
     <row r="15" spans="7:7">
       <c r="G15" t="s">
-        <v>119</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" ht="16.5" spans="7:7">
-      <c r="G16" s="1" t="s">
-        <v>120</v>
+      <c r="G16" s="2" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F46"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="19.875" style="1" customWidth="1"/>
+    <col min="2" max="2" width="15.375" style="1" customWidth="1"/>
+    <col min="3" max="3" width="34.5" style="1" customWidth="1"/>
+    <col min="4" max="4" width="86.75" style="2" customWidth="1"/>
+    <col min="5" max="6" width="19.25" style="1" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" s="1" customFormat="1" spans="1:4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" s="1" customFormat="1" spans="1:4">
+      <c r="A2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" spans="1:4">
+      <c r="A3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" s="1" customFormat="1" spans="1:4">
+      <c r="A4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" s="1" customFormat="1" spans="1:4">
+      <c r="A5" s="3">
+        <v>1</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="6" s="1" customFormat="1" spans="1:4">
+      <c r="A6" s="3">
+        <v>2</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" spans="1:4">
+      <c r="A7" s="3">
+        <v>3</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>51</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" s="1" customFormat="1" spans="1:4">
+      <c r="A8" s="3">
+        <v>4</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="9" s="1" customFormat="1" spans="1:4">
+      <c r="A9" s="3">
+        <v>5</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>56</v>
+      </c>
+    </row>
+    <row r="10" s="1" customFormat="1" spans="1:4">
+      <c r="A10" s="1">
+        <v>6</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>57</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="11" s="1" customFormat="1" spans="1:4">
+      <c r="A11" s="1">
+        <v>7</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:4">
+      <c r="A12" s="1">
+        <v>8</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="13" s="1" customFormat="1" spans="1:4">
+      <c r="A13" s="1">
+        <v>9</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C13" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="14" s="1" customFormat="1" spans="1:4">
+      <c r="A14" s="1">
+        <v>10</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="C14" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="15" s="1" customFormat="1" spans="1:4">
+      <c r="A15" s="1">
+        <v>11</v>
+      </c>
+      <c r="B15" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="16" s="1" customFormat="1" spans="1:4">
+      <c r="A16" s="1">
+        <v>12</v>
+      </c>
+      <c r="B16" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="17" s="1" customFormat="1" spans="1:6">
+      <c r="A17" s="1">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="18" s="1" customFormat="1" spans="1:6">
+      <c r="A18" s="1">
+        <v>14</v>
+      </c>
+      <c r="B18" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="C18" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="19" s="1" customFormat="1" spans="1:6">
+      <c r="A19" s="1">
+        <v>15</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C19" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="20" s="1" customFormat="1" spans="1:6">
+      <c r="A20" s="1">
+        <v>101</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="C20" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="21" s="1" customFormat="1" spans="1:6">
+      <c r="A21" s="1">
+        <v>102</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>81</v>
+      </c>
+      <c r="C21" s="1" t="s">
+        <v>82</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="22" s="1" customFormat="1" spans="1:6">
+      <c r="A22" s="1">
+        <v>103</v>
+      </c>
+      <c r="B22" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="C22" s="1" t="s">
+        <v>85</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="23" s="1" customFormat="1" spans="1:6">
+      <c r="A23" s="1">
+        <v>104</v>
+      </c>
+      <c r="B23" s="1" t="s">
+        <v>87</v>
+      </c>
+      <c r="C23" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>89</v>
+      </c>
+    </row>
+    <row r="24" s="1" customFormat="1" spans="1:6">
+      <c r="A24" s="1">
+        <v>105</v>
+      </c>
+      <c r="B24" s="1" t="s">
+        <v>90</v>
+      </c>
+      <c r="C24" s="1" t="s">
+        <v>91</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" s="1" customFormat="1" spans="1:6">
+      <c r="A25" s="1">
+        <v>201</v>
+      </c>
+      <c r="B25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="C25" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="26" s="1" customFormat="1" spans="1:6">
+      <c r="A26" s="1">
+        <v>202</v>
+      </c>
+      <c r="B26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="C26" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="27" s="1" customFormat="1" spans="1:6">
+      <c r="A27" s="1">
+        <v>203</v>
+      </c>
+      <c r="B27" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="C27" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" s="1" customFormat="1" spans="1:6">
+      <c r="A28" s="1">
+        <v>301</v>
+      </c>
+      <c r="B28" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="C28" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="29" s="1" customFormat="1" spans="1:6">
+      <c r="A29" s="1">
+        <v>15001</v>
+      </c>
+      <c r="B29" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="30" customFormat="1" spans="1:6">
+      <c r="A30" s="1">
+        <v>16001</v>
+      </c>
+      <c r="B30" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C30" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E30" s="1"/>
+      <c r="F30" s="1"/>
+    </row>
+    <row r="31" s="1" customFormat="1" spans="1:6">
+      <c r="A31" s="1">
+        <v>16002</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="32" s="1" customFormat="1" spans="1:6">
+      <c r="A32" s="1">
+        <v>16003</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="33" s="1" customFormat="1" spans="1:6">
+      <c r="A33" s="1">
+        <v>16004</v>
+      </c>
+      <c r="B33" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C33" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="34" s="1" customFormat="1" spans="1:6">
+      <c r="A34" s="1">
+        <v>16005</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C34" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="35" s="1" customFormat="1" spans="1:6">
+      <c r="A35" s="1">
+        <v>19001</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="36" s="1" customFormat="1" spans="1:6">
+      <c r="A36" s="1">
+        <v>19002</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>104</v>
+      </c>
+      <c r="C36" s="1" t="s">
+        <v>106</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="37" s="1" customFormat="1" spans="1:6">
+      <c r="A37" s="1">
+        <v>27001</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C37" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="38" s="1" customFormat="1" spans="1:6">
+      <c r="A38" s="1">
+        <v>27002</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="C38" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="39" s="1" customFormat="1" spans="1:6">
+      <c r="A39" s="1">
+        <v>28001</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="C39" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="40" s="1" customFormat="1" spans="1:6">
+      <c r="A40" s="1">
+        <v>29001</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C40" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="41" s="1" customFormat="1" spans="1:6">
+      <c r="A41" s="1">
+        <v>30001</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="C41" s="1" t="s">
+        <v>118</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="42" s="1" customFormat="1" spans="1:6">
+      <c r="A42" s="1">
+        <v>31001</v>
+      </c>
+      <c r="B42" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="C42" s="1" t="s">
+        <v>120</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="43" s="1" customFormat="1" spans="1:6">
+      <c r="A43" s="1">
+        <v>32001</v>
+      </c>
+      <c r="B43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="C43" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="D43" s="2" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="44" s="1" customFormat="1" spans="1:6">
+      <c r="A44" s="1">
+        <v>33001</v>
+      </c>
+      <c r="B44" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C44" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D44" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" s="1" customFormat="1" spans="1:6">
+      <c r="A45" s="1">
+        <v>34001</v>
+      </c>
+      <c r="B45" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="C45" s="1" t="s">
+        <v>125</v>
+      </c>
+      <c r="D45" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="46" customFormat="1" spans="1:6">
+      <c r="A46" s="1">
+        <v>401</v>
+      </c>
+      <c r="B46" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="C46" s="1" t="s">
+        <v>41</v>
+      </c>
+      <c r="D46" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="E46" s="1"/>
+      <c r="F46" s="1"/>
+    </row>
+  </sheetData>
+  <conditionalFormatting sqref="E5:F5">
+    <cfRule type="duplicateValues" dxfId="0" priority="4"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E6:F6">
+    <cfRule type="duplicateValues" dxfId="0" priority="3"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E9:F9">
+    <cfRule type="duplicateValues" dxfId="0" priority="1"/>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E7:F8">
+    <cfRule type="duplicateValues" dxfId="0" priority="2"/>
+  </conditionalFormatting>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
 </file>